--- a/sources/anna_step4.xlsx
+++ b/sources/anna_step4.xlsx
@@ -417,10 +417,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R136"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -428,7 +428,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -2216,7 +2216,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>d/f+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2246,210 +2246,210 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>+1 -5</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4,10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Does not work starting with d/f+1,2</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BT 1,2</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>BT 2,2</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>– Bermuda Triangle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
+          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>– 1,4,2 [~U_~D]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>– Snake [SS]</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>+1 0 +2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6,15,12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Does not work starting with d/f+1,2</t>
+          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>– Bermuda Triangle</t>
+          <t>–– High Kick</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2457,128 +2457,113 @@
           <t>h</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
+          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>–– u/f+3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>+1 0 +2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
+          <t>–– Bone Cutter</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6,15,12</t>
+          <t>13,10,10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>hhh</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
+          <t>h</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
+          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>–– High Kick</t>
+          <t>–– Spin Trip</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
+          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
+          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -2590,163 +2575,183 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>–– u/f+3</t>
+          <t>– 1,b+4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>–– Bone Cutter</t>
+          <t>– Jab Rush - Low Kick</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>+1 -10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>13,10,10</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>hl</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>–– 4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>–– Spin Trip</t>
+          <t>PDK Combo</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>+1 -10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
+          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>– 1,b+4</t>
+          <t>d/f+1,2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>– Jab Rush - Low Kick</t>
+          <t>Double Punch</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>+1 +1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
+          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>BT 1,2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BT 2,2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PDK Combo</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2756,42 +2761,37 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>-8 -5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>15,10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
+          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
+          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
         </is>
       </c>
     </row>
@@ -6748,65 +6748,6 @@
         </is>
       </c>
       <c r="R134" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>d/f+1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>3868d410-2e89-48d9-953a-b6d47bab49c4</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>BT 1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>2f43bade-2f95-4531-9ea3-4cdbb2bdd0bd</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/anna_step4.xlsx
+++ b/sources/anna_step4.xlsx
@@ -790,6 +790,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
@@ -832,6 +837,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
@@ -872,6 +882,11 @@
       <c r="L10" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>31ad5619-ed1a-41f7-95e0-e44eadc9aed1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -6319,6 +6334,11 @@
           <t>Special Tag Throw with Nina only. Nina finishes with a Reverse Shoulder Lock. Total damage is 15,30.</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
@@ -6351,6 +6371,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
@@ -6388,6 +6413,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
@@ -6425,6 +6455,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
@@ -6462,6 +6497,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
@@ -6499,6 +6539,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
@@ -6536,6 +6581,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
@@ -6573,6 +6623,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>93714c88-336b-411f-b863-f65c2a39733a</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
@@ -6608,6 +6663,11 @@
       <c r="L130" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>0e938de5-6095-4002-9ade-581f69b50247</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -6740,6 +6800,11 @@
       <c r="J134" t="inlineStr">
         <is>
           <t>hhhhhlhhhh</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>d61c2d77-39a1-494e-8996-5a62586356a9</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">

--- a/sources/anna_step4.xlsx
+++ b/sources/anna_step4.xlsx
@@ -2593,6 +2593,11 @@
           <t>– 1,b+4</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1,d/b+4; 1,d+4</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>– Jab Rush - Low Kick</t>
